--- a/public/templates/otzar_hakodesh_books_import_template.xlsx
+++ b/public/templates/otzar_hakodesh_books_import_template.xlsx
@@ -804,7 +804,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:T3"/>
+  <dimension ref="A1:T2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1033,100 +1033,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="8" t="inlineStr">
-        <is>
-          <t>001</t>
-        </is>
-      </c>
-      <c r="B3" s="8" t="inlineStr">
-        <is>
-          <t>7290000000011</t>
-        </is>
-      </c>
-      <c r="C3" s="8" t="inlineStr">
-        <is>
-          <t>חומשים לדוגמה</t>
-        </is>
-      </c>
-      <c r="D3" s="8" t="inlineStr">
-        <is>
-          <t>תת קטגוריה לדוגמה</t>
-        </is>
-      </c>
-      <c r="E3" s="8" t="inlineStr">
-        <is>
-          <t>ספרי יסוד|מומלצים</t>
-        </is>
-      </c>
-      <c r="F3" s="8" t="inlineStr">
-        <is>
-          <t>מחבר לדוגמה</t>
-        </is>
-      </c>
-      <c r="G3" s="8" t="inlineStr">
-        <is>
-          <t>רב לדוגמה</t>
-        </is>
-      </c>
-      <c r="H3" s="8" t="inlineStr">
-        <is>
-          <t>הוצאה לדוגמה</t>
-        </is>
-      </c>
-      <c r="I3" s="8" t="inlineStr">
-        <is>
-          <t>תיאור קצר שיופיע בכרטיס המוצר</t>
-        </is>
-      </c>
-      <c r="J3" s="8" t="inlineStr">
-        <is>
-          <t>תיאור מפורט שיופיע בדף המוצר</t>
-        </is>
-      </c>
-      <c r="K3" s="8" t="n">
-        <v>120</v>
-      </c>
-      <c r="L3" s="8" t="n">
-        <v>99</v>
-      </c>
-      <c r="M3" s="8" t="n">
-        <v>25</v>
-      </c>
-      <c r="N3" s="8" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="O3" s="8" t="inlineStr">
-        <is>
-          <t>עברית</t>
-        </is>
-      </c>
-      <c r="P3" s="8" t="inlineStr">
-        <is>
-          <t>001.jpg</t>
-        </is>
-      </c>
-      <c r="Q3" s="8" t="inlineStr">
-        <is>
-          <t>כן</t>
-        </is>
-      </c>
-      <c r="R3" s="8" t="inlineStr">
-        <is>
-          <t>לא</t>
-        </is>
-      </c>
-      <c r="S3" s="8" t="inlineStr">
-        <is>
-          <t>כן</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="inlineStr">
-        <is>
-          <t>כן</t>
-        </is>
-      </c>
-    </row>
+    <row r="3" ht="24" customHeight="1"/>
     <row r="4" ht="24" customHeight="1"/>
     <row r="5" ht="24" customHeight="1"/>
     <row r="6" ht="24" customHeight="1"/>
@@ -3145,7 +3052,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:T3"/>
+  <dimension ref="A1:T2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3374,100 +3281,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="8" t="inlineStr">
-        <is>
-          <t>001</t>
-        </is>
-      </c>
-      <c r="B3" s="8" t="inlineStr">
-        <is>
-          <t>7290000000011</t>
-        </is>
-      </c>
-      <c r="C3" s="8" t="inlineStr">
-        <is>
-          <t>גמרות ומשניות לדוגמה</t>
-        </is>
-      </c>
-      <c r="D3" s="8" t="inlineStr">
-        <is>
-          <t>תת קטגוריה לדוגמה</t>
-        </is>
-      </c>
-      <c r="E3" s="8" t="inlineStr">
-        <is>
-          <t>ספרי יסוד|מומלצים</t>
-        </is>
-      </c>
-      <c r="F3" s="8" t="inlineStr">
-        <is>
-          <t>מחבר לדוגמה</t>
-        </is>
-      </c>
-      <c r="G3" s="8" t="inlineStr">
-        <is>
-          <t>רב לדוגמה</t>
-        </is>
-      </c>
-      <c r="H3" s="8" t="inlineStr">
-        <is>
-          <t>הוצאה לדוגמה</t>
-        </is>
-      </c>
-      <c r="I3" s="8" t="inlineStr">
-        <is>
-          <t>תיאור קצר שיופיע בכרטיס המוצר</t>
-        </is>
-      </c>
-      <c r="J3" s="8" t="inlineStr">
-        <is>
-          <t>תיאור מפורט שיופיע בדף המוצר</t>
-        </is>
-      </c>
-      <c r="K3" s="8" t="n">
-        <v>120</v>
-      </c>
-      <c r="L3" s="8" t="n">
-        <v>99</v>
-      </c>
-      <c r="M3" s="8" t="n">
-        <v>25</v>
-      </c>
-      <c r="N3" s="8" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="O3" s="8" t="inlineStr">
-        <is>
-          <t>עברית</t>
-        </is>
-      </c>
-      <c r="P3" s="8" t="inlineStr">
-        <is>
-          <t>001.jpg</t>
-        </is>
-      </c>
-      <c r="Q3" s="8" t="inlineStr">
-        <is>
-          <t>כן</t>
-        </is>
-      </c>
-      <c r="R3" s="8" t="inlineStr">
-        <is>
-          <t>לא</t>
-        </is>
-      </c>
-      <c r="S3" s="8" t="inlineStr">
-        <is>
-          <t>כן</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="inlineStr">
-        <is>
-          <t>כן</t>
-        </is>
-      </c>
-    </row>
+    <row r="3" ht="24" customHeight="1"/>
     <row r="4" ht="24" customHeight="1"/>
     <row r="5" ht="24" customHeight="1"/>
     <row r="6" ht="24" customHeight="1"/>
@@ -5486,7 +5300,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:T3"/>
+  <dimension ref="A1:T2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5715,100 +5529,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="8" t="inlineStr">
-        <is>
-          <t>001</t>
-        </is>
-      </c>
-      <c r="B3" s="8" t="inlineStr">
-        <is>
-          <t>7290000000011</t>
-        </is>
-      </c>
-      <c r="C3" s="8" t="inlineStr">
-        <is>
-          <t>הלכה לדוגמה</t>
-        </is>
-      </c>
-      <c r="D3" s="8" t="inlineStr">
-        <is>
-          <t>תת קטגוריה לדוגמה</t>
-        </is>
-      </c>
-      <c r="E3" s="8" t="inlineStr">
-        <is>
-          <t>ספרי יסוד|מומלצים</t>
-        </is>
-      </c>
-      <c r="F3" s="8" t="inlineStr">
-        <is>
-          <t>מחבר לדוגמה</t>
-        </is>
-      </c>
-      <c r="G3" s="8" t="inlineStr">
-        <is>
-          <t>רב לדוגמה</t>
-        </is>
-      </c>
-      <c r="H3" s="8" t="inlineStr">
-        <is>
-          <t>הוצאה לדוגמה</t>
-        </is>
-      </c>
-      <c r="I3" s="8" t="inlineStr">
-        <is>
-          <t>תיאור קצר שיופיע בכרטיס המוצר</t>
-        </is>
-      </c>
-      <c r="J3" s="8" t="inlineStr">
-        <is>
-          <t>תיאור מפורט שיופיע בדף המוצר</t>
-        </is>
-      </c>
-      <c r="K3" s="8" t="n">
-        <v>120</v>
-      </c>
-      <c r="L3" s="8" t="n">
-        <v>99</v>
-      </c>
-      <c r="M3" s="8" t="n">
-        <v>25</v>
-      </c>
-      <c r="N3" s="8" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="O3" s="8" t="inlineStr">
-        <is>
-          <t>עברית</t>
-        </is>
-      </c>
-      <c r="P3" s="8" t="inlineStr">
-        <is>
-          <t>001.jpg</t>
-        </is>
-      </c>
-      <c r="Q3" s="8" t="inlineStr">
-        <is>
-          <t>כן</t>
-        </is>
-      </c>
-      <c r="R3" s="8" t="inlineStr">
-        <is>
-          <t>לא</t>
-        </is>
-      </c>
-      <c r="S3" s="8" t="inlineStr">
-        <is>
-          <t>כן</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="inlineStr">
-        <is>
-          <t>כן</t>
-        </is>
-      </c>
-    </row>
+    <row r="3" ht="24" customHeight="1"/>
     <row r="4" ht="24" customHeight="1"/>
     <row r="5" ht="24" customHeight="1"/>
     <row r="6" ht="24" customHeight="1"/>
@@ -7827,7 +7548,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:T3"/>
+  <dimension ref="A1:T2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -8056,100 +7777,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="8" t="inlineStr">
-        <is>
-          <t>001</t>
-        </is>
-      </c>
-      <c r="B3" s="8" t="inlineStr">
-        <is>
-          <t>7290000000011</t>
-        </is>
-      </c>
-      <c r="C3" s="8" t="inlineStr">
-        <is>
-          <t>חסידות וקבלה לדוגמה</t>
-        </is>
-      </c>
-      <c r="D3" s="8" t="inlineStr">
-        <is>
-          <t>תת קטגוריה לדוגמה</t>
-        </is>
-      </c>
-      <c r="E3" s="8" t="inlineStr">
-        <is>
-          <t>ספרי יסוד|מומלצים</t>
-        </is>
-      </c>
-      <c r="F3" s="8" t="inlineStr">
-        <is>
-          <t>מחבר לדוגמה</t>
-        </is>
-      </c>
-      <c r="G3" s="8" t="inlineStr">
-        <is>
-          <t>רב לדוגמה</t>
-        </is>
-      </c>
-      <c r="H3" s="8" t="inlineStr">
-        <is>
-          <t>הוצאה לדוגמה</t>
-        </is>
-      </c>
-      <c r="I3" s="8" t="inlineStr">
-        <is>
-          <t>תיאור קצר שיופיע בכרטיס המוצר</t>
-        </is>
-      </c>
-      <c r="J3" s="8" t="inlineStr">
-        <is>
-          <t>תיאור מפורט שיופיע בדף המוצר</t>
-        </is>
-      </c>
-      <c r="K3" s="8" t="n">
-        <v>120</v>
-      </c>
-      <c r="L3" s="8" t="n">
-        <v>99</v>
-      </c>
-      <c r="M3" s="8" t="n">
-        <v>25</v>
-      </c>
-      <c r="N3" s="8" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="O3" s="8" t="inlineStr">
-        <is>
-          <t>עברית</t>
-        </is>
-      </c>
-      <c r="P3" s="8" t="inlineStr">
-        <is>
-          <t>001.jpg</t>
-        </is>
-      </c>
-      <c r="Q3" s="8" t="inlineStr">
-        <is>
-          <t>כן</t>
-        </is>
-      </c>
-      <c r="R3" s="8" t="inlineStr">
-        <is>
-          <t>לא</t>
-        </is>
-      </c>
-      <c r="S3" s="8" t="inlineStr">
-        <is>
-          <t>כן</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="inlineStr">
-        <is>
-          <t>כן</t>
-        </is>
-      </c>
-    </row>
+    <row r="3" ht="24" customHeight="1"/>
     <row r="4" ht="24" customHeight="1"/>
     <row r="5" ht="24" customHeight="1"/>
     <row r="6" ht="24" customHeight="1"/>
@@ -10168,7 +9796,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:T3"/>
+  <dimension ref="A1:T2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -10397,100 +10025,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="8" t="inlineStr">
-        <is>
-          <t>001</t>
-        </is>
-      </c>
-      <c r="B3" s="8" t="inlineStr">
-        <is>
-          <t>7290000000011</t>
-        </is>
-      </c>
-      <c r="C3" s="8" t="inlineStr">
-        <is>
-          <t>ספרי ילדים ונוער לדוגמה</t>
-        </is>
-      </c>
-      <c r="D3" s="8" t="inlineStr">
-        <is>
-          <t>תת קטגוריה לדוגמה</t>
-        </is>
-      </c>
-      <c r="E3" s="8" t="inlineStr">
-        <is>
-          <t>ספרי יסוד|מומלצים</t>
-        </is>
-      </c>
-      <c r="F3" s="8" t="inlineStr">
-        <is>
-          <t>מחבר לדוגמה</t>
-        </is>
-      </c>
-      <c r="G3" s="8" t="inlineStr">
-        <is>
-          <t>רב לדוגמה</t>
-        </is>
-      </c>
-      <c r="H3" s="8" t="inlineStr">
-        <is>
-          <t>הוצאה לדוגמה</t>
-        </is>
-      </c>
-      <c r="I3" s="8" t="inlineStr">
-        <is>
-          <t>תיאור קצר שיופיע בכרטיס המוצר</t>
-        </is>
-      </c>
-      <c r="J3" s="8" t="inlineStr">
-        <is>
-          <t>תיאור מפורט שיופיע בדף המוצר</t>
-        </is>
-      </c>
-      <c r="K3" s="8" t="n">
-        <v>120</v>
-      </c>
-      <c r="L3" s="8" t="n">
-        <v>99</v>
-      </c>
-      <c r="M3" s="8" t="n">
-        <v>25</v>
-      </c>
-      <c r="N3" s="8" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="O3" s="8" t="inlineStr">
-        <is>
-          <t>עברית</t>
-        </is>
-      </c>
-      <c r="P3" s="8" t="inlineStr">
-        <is>
-          <t>001.jpg</t>
-        </is>
-      </c>
-      <c r="Q3" s="8" t="inlineStr">
-        <is>
-          <t>כן</t>
-        </is>
-      </c>
-      <c r="R3" s="8" t="inlineStr">
-        <is>
-          <t>לא</t>
-        </is>
-      </c>
-      <c r="S3" s="8" t="inlineStr">
-        <is>
-          <t>כן</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="inlineStr">
-        <is>
-          <t>כן</t>
-        </is>
-      </c>
-    </row>
+    <row r="3" ht="24" customHeight="1"/>
     <row r="4" ht="24" customHeight="1"/>
     <row r="5" ht="24" customHeight="1"/>
     <row r="6" ht="24" customHeight="1"/>
@@ -12509,7 +12044,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:T3"/>
+  <dimension ref="A1:T2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -12738,100 +12273,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="8" t="inlineStr">
-        <is>
-          <t>001</t>
-        </is>
-      </c>
-      <c r="B3" s="8" t="inlineStr">
-        <is>
-          <t>7290000000011</t>
-        </is>
-      </c>
-      <c r="C3" s="8" t="inlineStr">
-        <is>
-          <t>מוסר ומחשבה לדוגמה</t>
-        </is>
-      </c>
-      <c r="D3" s="8" t="inlineStr">
-        <is>
-          <t>תת קטגוריה לדוגמה</t>
-        </is>
-      </c>
-      <c r="E3" s="8" t="inlineStr">
-        <is>
-          <t>ספרי יסוד|מומלצים</t>
-        </is>
-      </c>
-      <c r="F3" s="8" t="inlineStr">
-        <is>
-          <t>מחבר לדוגמה</t>
-        </is>
-      </c>
-      <c r="G3" s="8" t="inlineStr">
-        <is>
-          <t>רב לדוגמה</t>
-        </is>
-      </c>
-      <c r="H3" s="8" t="inlineStr">
-        <is>
-          <t>הוצאה לדוגמה</t>
-        </is>
-      </c>
-      <c r="I3" s="8" t="inlineStr">
-        <is>
-          <t>תיאור קצר שיופיע בכרטיס המוצר</t>
-        </is>
-      </c>
-      <c r="J3" s="8" t="inlineStr">
-        <is>
-          <t>תיאור מפורט שיופיע בדף המוצר</t>
-        </is>
-      </c>
-      <c r="K3" s="8" t="n">
-        <v>120</v>
-      </c>
-      <c r="L3" s="8" t="n">
-        <v>99</v>
-      </c>
-      <c r="M3" s="8" t="n">
-        <v>25</v>
-      </c>
-      <c r="N3" s="8" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="O3" s="8" t="inlineStr">
-        <is>
-          <t>עברית</t>
-        </is>
-      </c>
-      <c r="P3" s="8" t="inlineStr">
-        <is>
-          <t>001.jpg</t>
-        </is>
-      </c>
-      <c r="Q3" s="8" t="inlineStr">
-        <is>
-          <t>כן</t>
-        </is>
-      </c>
-      <c r="R3" s="8" t="inlineStr">
-        <is>
-          <t>לא</t>
-        </is>
-      </c>
-      <c r="S3" s="8" t="inlineStr">
-        <is>
-          <t>כן</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="inlineStr">
-        <is>
-          <t>כן</t>
-        </is>
-      </c>
-    </row>
+    <row r="3" ht="24" customHeight="1"/>
     <row r="4" ht="24" customHeight="1"/>
     <row r="5" ht="24" customHeight="1"/>
     <row r="6" ht="24" customHeight="1"/>
@@ -14850,7 +14292,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:T3"/>
+  <dimension ref="A1:T2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -15079,100 +14521,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="8" t="inlineStr">
-        <is>
-          <t>001</t>
-        </is>
-      </c>
-      <c r="B3" s="8" t="inlineStr">
-        <is>
-          <t>7290000000011</t>
-        </is>
-      </c>
-      <c r="C3" s="8" t="inlineStr">
-        <is>
-          <t>ספרי הרב עובדיה יוסף לדוגמה</t>
-        </is>
-      </c>
-      <c r="D3" s="8" t="inlineStr">
-        <is>
-          <t>תת קטגוריה לדוגמה</t>
-        </is>
-      </c>
-      <c r="E3" s="8" t="inlineStr">
-        <is>
-          <t>ספרי יסוד|מומלצים</t>
-        </is>
-      </c>
-      <c r="F3" s="8" t="inlineStr">
-        <is>
-          <t>מחבר לדוגמה</t>
-        </is>
-      </c>
-      <c r="G3" s="8" t="inlineStr">
-        <is>
-          <t>רב לדוגמה</t>
-        </is>
-      </c>
-      <c r="H3" s="8" t="inlineStr">
-        <is>
-          <t>הוצאה לדוגמה</t>
-        </is>
-      </c>
-      <c r="I3" s="8" t="inlineStr">
-        <is>
-          <t>תיאור קצר שיופיע בכרטיס המוצר</t>
-        </is>
-      </c>
-      <c r="J3" s="8" t="inlineStr">
-        <is>
-          <t>תיאור מפורט שיופיע בדף המוצר</t>
-        </is>
-      </c>
-      <c r="K3" s="8" t="n">
-        <v>120</v>
-      </c>
-      <c r="L3" s="8" t="n">
-        <v>99</v>
-      </c>
-      <c r="M3" s="8" t="n">
-        <v>25</v>
-      </c>
-      <c r="N3" s="8" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="O3" s="8" t="inlineStr">
-        <is>
-          <t>עברית</t>
-        </is>
-      </c>
-      <c r="P3" s="8" t="inlineStr">
-        <is>
-          <t>001.jpg</t>
-        </is>
-      </c>
-      <c r="Q3" s="8" t="inlineStr">
-        <is>
-          <t>כן</t>
-        </is>
-      </c>
-      <c r="R3" s="8" t="inlineStr">
-        <is>
-          <t>לא</t>
-        </is>
-      </c>
-      <c r="S3" s="8" t="inlineStr">
-        <is>
-          <t>כן</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="inlineStr">
-        <is>
-          <t>כן</t>
-        </is>
-      </c>
-    </row>
+    <row r="3" ht="24" customHeight="1"/>
     <row r="4" ht="24" customHeight="1"/>
     <row r="5" ht="24" customHeight="1"/>
     <row r="6" ht="24" customHeight="1"/>
@@ -17191,7 +16540,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:T3"/>
+  <dimension ref="A1:T2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -17420,100 +16769,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="8" t="inlineStr">
-        <is>
-          <t>001</t>
-        </is>
-      </c>
-      <c r="B3" s="8" t="inlineStr">
-        <is>
-          <t>7290000000011</t>
-        </is>
-      </c>
-      <c r="C3" s="8" t="inlineStr">
-        <is>
-          <t>ספרי חב"ד לדוגמה</t>
-        </is>
-      </c>
-      <c r="D3" s="8" t="inlineStr">
-        <is>
-          <t>תת קטגוריה לדוגמה</t>
-        </is>
-      </c>
-      <c r="E3" s="8" t="inlineStr">
-        <is>
-          <t>ספרי יסוד|מומלצים</t>
-        </is>
-      </c>
-      <c r="F3" s="8" t="inlineStr">
-        <is>
-          <t>מחבר לדוגמה</t>
-        </is>
-      </c>
-      <c r="G3" s="8" t="inlineStr">
-        <is>
-          <t>רב לדוגמה</t>
-        </is>
-      </c>
-      <c r="H3" s="8" t="inlineStr">
-        <is>
-          <t>הוצאה לדוגמה</t>
-        </is>
-      </c>
-      <c r="I3" s="8" t="inlineStr">
-        <is>
-          <t>תיאור קצר שיופיע בכרטיס המוצר</t>
-        </is>
-      </c>
-      <c r="J3" s="8" t="inlineStr">
-        <is>
-          <t>תיאור מפורט שיופיע בדף המוצר</t>
-        </is>
-      </c>
-      <c r="K3" s="8" t="n">
-        <v>120</v>
-      </c>
-      <c r="L3" s="8" t="n">
-        <v>99</v>
-      </c>
-      <c r="M3" s="8" t="n">
-        <v>25</v>
-      </c>
-      <c r="N3" s="8" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="O3" s="8" t="inlineStr">
-        <is>
-          <t>עברית</t>
-        </is>
-      </c>
-      <c r="P3" s="8" t="inlineStr">
-        <is>
-          <t>001.jpg</t>
-        </is>
-      </c>
-      <c r="Q3" s="8" t="inlineStr">
-        <is>
-          <t>כן</t>
-        </is>
-      </c>
-      <c r="R3" s="8" t="inlineStr">
-        <is>
-          <t>לא</t>
-        </is>
-      </c>
-      <c r="S3" s="8" t="inlineStr">
-        <is>
-          <t>כן</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="inlineStr">
-        <is>
-          <t>כן</t>
-        </is>
-      </c>
-    </row>
+    <row r="3" ht="24" customHeight="1"/>
     <row r="4" ht="24" customHeight="1"/>
     <row r="5" ht="24" customHeight="1"/>
     <row r="6" ht="24" customHeight="1"/>

--- a/public/templates/otzar_hakodesh_books_import_template.xlsx
+++ b/public/templates/otzar_hakodesh_books_import_template.xlsx
@@ -17,14 +17,14 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ספרי חב&quot;ד" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'חומשים'!$A$1:$T$10000</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'גמרות ומשניות'!$A$1:$T$10000</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'הלכה'!$A$1:$T$10000</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'חסידות וקבלה'!$A$1:$T$10000</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'ספרי ילדים ונוער'!$A$1:$T$10000</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'מוסר ומחשבה'!$A$1:$T$10000</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'ספרי הרב עובדיה יוסף'!$A$1:$T$10000</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'ספרי חב"ד'!$A$1:$T$10000</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'חומשים'!$A$1:$J$10000</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'גמרות ומשניות'!$A$1:$J$10000</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'הלכה'!$A$1:$J$10000</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'חסידות וקבלה'!$A$1:$J$10000</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'ספרי ילדים ונוער'!$A$1:$J$10000</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'מוסר ומחשבה'!$A$1:$J$10000</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'ספרי הרב עובדיה יוסף'!$A$1:$J$10000</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'ספרי חב"ד'!$A$1:$J$10000</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -62,7 +62,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001D4ED8"/>
+        <fgColor rgb="002563EB"/>
       </patternFill>
     </fill>
   </fills>
@@ -86,10 +86,10 @@
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -456,29 +456,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:T1"/>
+  <dimension ref="A1:J1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="28" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="34" customWidth="1" min="9" max="9"/>
-    <col width="44" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="16" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="12" customWidth="1" min="15" max="15"/>
-    <col width="22" customWidth="1" min="16" max="16"/>
-    <col width="18" customWidth="1" min="17" max="17"/>
-    <col width="12" customWidth="1" min="18" max="18"/>
-    <col width="10" customWidth="1" min="19" max="19"/>
-    <col width="10" customWidth="1" min="20" max="20"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -499,100 +489,42 @@
       </c>
       <c r="D1" s="2" t="inlineStr">
         <is>
-          <t>תת קטגוריה</t>
+          <t>מחבר / רב</t>
         </is>
       </c>
       <c r="E1" s="2" t="inlineStr">
         <is>
-          <t>קטגוריות נוספות</t>
+          <t>הוצאה לאור</t>
         </is>
       </c>
       <c r="F1" s="2" t="inlineStr">
         <is>
-          <t>מחבר</t>
-        </is>
-      </c>
-      <c r="G1" s="2" t="inlineStr">
-        <is>
-          <t>רב</t>
+          <t>תיאור</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>מחיר</t>
         </is>
       </c>
       <c r="H1" s="2" t="inlineStr">
         <is>
-          <t>הוצאה לאור</t>
+          <t>מחיר מבצע</t>
         </is>
       </c>
       <c r="I1" s="2" t="inlineStr">
         <is>
-          <t>תיאור קצר</t>
+          <t>מלאי</t>
         </is>
       </c>
       <c r="J1" s="2" t="inlineStr">
         <is>
-          <t>תיאור ארוך</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>מחיר</t>
-        </is>
-      </c>
-      <c r="L1" s="2" t="inlineStr">
-        <is>
-          <t>מחיר מבצע</t>
-        </is>
-      </c>
-      <c r="M1" s="2" t="inlineStr">
-        <is>
-          <t>כמות במלאי</t>
-        </is>
-      </c>
-      <c r="N1" s="2" t="inlineStr">
-        <is>
-          <t>משקל</t>
-        </is>
-      </c>
-      <c r="O1" s="2" t="inlineStr">
-        <is>
-          <t>שפה</t>
-        </is>
-      </c>
-      <c r="P1" s="2" t="inlineStr">
-        <is>
-          <t>שם קובץ תמונה</t>
-        </is>
-      </c>
-      <c r="Q1" s="2" t="inlineStr">
-        <is>
-          <t>מוצג בדף הבית</t>
-        </is>
-      </c>
-      <c r="R1" s="2" t="inlineStr">
-        <is>
-          <t>מומלץ</t>
-        </is>
-      </c>
-      <c r="S1" s="2" t="inlineStr">
-        <is>
-          <t>חדש</t>
-        </is>
-      </c>
-      <c r="T1" s="2" t="inlineStr">
-        <is>
-          <t>פעיל</t>
+          <t>תמונה</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T10000"/>
-  <dataValidations count="2">
-    <dataValidation sqref="Q2:T10000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"כן,לא"</formula1>
-    </dataValidation>
-    <dataValidation sqref="O2:O10000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"עברית,אנגלית,יידיש,ארמית"</formula1>
-    </dataValidation>
-  </dataValidations>
+  <autoFilter ref="A1:J10000"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
@@ -604,29 +536,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:T1"/>
+  <dimension ref="A1:J1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="28" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="34" customWidth="1" min="9" max="9"/>
-    <col width="44" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="16" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="12" customWidth="1" min="15" max="15"/>
-    <col width="22" customWidth="1" min="16" max="16"/>
-    <col width="18" customWidth="1" min="17" max="17"/>
-    <col width="12" customWidth="1" min="18" max="18"/>
-    <col width="10" customWidth="1" min="19" max="19"/>
-    <col width="10" customWidth="1" min="20" max="20"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -647,100 +569,42 @@
       </c>
       <c r="D1" s="2" t="inlineStr">
         <is>
-          <t>תת קטגוריה</t>
+          <t>מחבר / רב</t>
         </is>
       </c>
       <c r="E1" s="2" t="inlineStr">
         <is>
-          <t>קטגוריות נוספות</t>
+          <t>הוצאה לאור</t>
         </is>
       </c>
       <c r="F1" s="2" t="inlineStr">
         <is>
-          <t>מחבר</t>
-        </is>
-      </c>
-      <c r="G1" s="2" t="inlineStr">
-        <is>
-          <t>רב</t>
+          <t>תיאור</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>מחיר</t>
         </is>
       </c>
       <c r="H1" s="2" t="inlineStr">
         <is>
-          <t>הוצאה לאור</t>
+          <t>מחיר מבצע</t>
         </is>
       </c>
       <c r="I1" s="2" t="inlineStr">
         <is>
-          <t>תיאור קצר</t>
+          <t>מלאי</t>
         </is>
       </c>
       <c r="J1" s="2" t="inlineStr">
         <is>
-          <t>תיאור ארוך</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>מחיר</t>
-        </is>
-      </c>
-      <c r="L1" s="2" t="inlineStr">
-        <is>
-          <t>מחיר מבצע</t>
-        </is>
-      </c>
-      <c r="M1" s="2" t="inlineStr">
-        <is>
-          <t>כמות במלאי</t>
-        </is>
-      </c>
-      <c r="N1" s="2" t="inlineStr">
-        <is>
-          <t>משקל</t>
-        </is>
-      </c>
-      <c r="O1" s="2" t="inlineStr">
-        <is>
-          <t>שפה</t>
-        </is>
-      </c>
-      <c r="P1" s="2" t="inlineStr">
-        <is>
-          <t>שם קובץ תמונה</t>
-        </is>
-      </c>
-      <c r="Q1" s="2" t="inlineStr">
-        <is>
-          <t>מוצג בדף הבית</t>
-        </is>
-      </c>
-      <c r="R1" s="2" t="inlineStr">
-        <is>
-          <t>מומלץ</t>
-        </is>
-      </c>
-      <c r="S1" s="2" t="inlineStr">
-        <is>
-          <t>חדש</t>
-        </is>
-      </c>
-      <c r="T1" s="2" t="inlineStr">
-        <is>
-          <t>פעיל</t>
+          <t>תמונה</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T10000"/>
-  <dataValidations count="2">
-    <dataValidation sqref="Q2:T10000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"כן,לא"</formula1>
-    </dataValidation>
-    <dataValidation sqref="O2:O10000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"עברית,אנגלית,יידיש,ארמית"</formula1>
-    </dataValidation>
-  </dataValidations>
+  <autoFilter ref="A1:J10000"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
@@ -752,29 +616,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:T1"/>
+  <dimension ref="A1:J1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="28" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="34" customWidth="1" min="9" max="9"/>
-    <col width="44" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="16" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="12" customWidth="1" min="15" max="15"/>
-    <col width="22" customWidth="1" min="16" max="16"/>
-    <col width="18" customWidth="1" min="17" max="17"/>
-    <col width="12" customWidth="1" min="18" max="18"/>
-    <col width="10" customWidth="1" min="19" max="19"/>
-    <col width="10" customWidth="1" min="20" max="20"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -795,100 +649,42 @@
       </c>
       <c r="D1" s="2" t="inlineStr">
         <is>
-          <t>תת קטגוריה</t>
+          <t>מחבר / רב</t>
         </is>
       </c>
       <c r="E1" s="2" t="inlineStr">
         <is>
-          <t>קטגוריות נוספות</t>
+          <t>הוצאה לאור</t>
         </is>
       </c>
       <c r="F1" s="2" t="inlineStr">
         <is>
-          <t>מחבר</t>
-        </is>
-      </c>
-      <c r="G1" s="2" t="inlineStr">
-        <is>
-          <t>רב</t>
+          <t>תיאור</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>מחיר</t>
         </is>
       </c>
       <c r="H1" s="2" t="inlineStr">
         <is>
-          <t>הוצאה לאור</t>
+          <t>מחיר מבצע</t>
         </is>
       </c>
       <c r="I1" s="2" t="inlineStr">
         <is>
-          <t>תיאור קצר</t>
+          <t>מלאי</t>
         </is>
       </c>
       <c r="J1" s="2" t="inlineStr">
         <is>
-          <t>תיאור ארוך</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>מחיר</t>
-        </is>
-      </c>
-      <c r="L1" s="2" t="inlineStr">
-        <is>
-          <t>מחיר מבצע</t>
-        </is>
-      </c>
-      <c r="M1" s="2" t="inlineStr">
-        <is>
-          <t>כמות במלאי</t>
-        </is>
-      </c>
-      <c r="N1" s="2" t="inlineStr">
-        <is>
-          <t>משקל</t>
-        </is>
-      </c>
-      <c r="O1" s="2" t="inlineStr">
-        <is>
-          <t>שפה</t>
-        </is>
-      </c>
-      <c r="P1" s="2" t="inlineStr">
-        <is>
-          <t>שם קובץ תמונה</t>
-        </is>
-      </c>
-      <c r="Q1" s="2" t="inlineStr">
-        <is>
-          <t>מוצג בדף הבית</t>
-        </is>
-      </c>
-      <c r="R1" s="2" t="inlineStr">
-        <is>
-          <t>מומלץ</t>
-        </is>
-      </c>
-      <c r="S1" s="2" t="inlineStr">
-        <is>
-          <t>חדש</t>
-        </is>
-      </c>
-      <c r="T1" s="2" t="inlineStr">
-        <is>
-          <t>פעיל</t>
+          <t>תמונה</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T10000"/>
-  <dataValidations count="2">
-    <dataValidation sqref="Q2:T10000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"כן,לא"</formula1>
-    </dataValidation>
-    <dataValidation sqref="O2:O10000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"עברית,אנגלית,יידיש,ארמית"</formula1>
-    </dataValidation>
-  </dataValidations>
+  <autoFilter ref="A1:J10000"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
@@ -900,29 +696,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:T1"/>
+  <dimension ref="A1:J1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="28" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="34" customWidth="1" min="9" max="9"/>
-    <col width="44" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="16" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="12" customWidth="1" min="15" max="15"/>
-    <col width="22" customWidth="1" min="16" max="16"/>
-    <col width="18" customWidth="1" min="17" max="17"/>
-    <col width="12" customWidth="1" min="18" max="18"/>
-    <col width="10" customWidth="1" min="19" max="19"/>
-    <col width="10" customWidth="1" min="20" max="20"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -943,100 +729,42 @@
       </c>
       <c r="D1" s="2" t="inlineStr">
         <is>
-          <t>תת קטגוריה</t>
+          <t>מחבר / רב</t>
         </is>
       </c>
       <c r="E1" s="2" t="inlineStr">
         <is>
-          <t>קטגוריות נוספות</t>
+          <t>הוצאה לאור</t>
         </is>
       </c>
       <c r="F1" s="2" t="inlineStr">
         <is>
-          <t>מחבר</t>
-        </is>
-      </c>
-      <c r="G1" s="2" t="inlineStr">
-        <is>
-          <t>רב</t>
+          <t>תיאור</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>מחיר</t>
         </is>
       </c>
       <c r="H1" s="2" t="inlineStr">
         <is>
-          <t>הוצאה לאור</t>
+          <t>מחיר מבצע</t>
         </is>
       </c>
       <c r="I1" s="2" t="inlineStr">
         <is>
-          <t>תיאור קצר</t>
+          <t>מלאי</t>
         </is>
       </c>
       <c r="J1" s="2" t="inlineStr">
         <is>
-          <t>תיאור ארוך</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>מחיר</t>
-        </is>
-      </c>
-      <c r="L1" s="2" t="inlineStr">
-        <is>
-          <t>מחיר מבצע</t>
-        </is>
-      </c>
-      <c r="M1" s="2" t="inlineStr">
-        <is>
-          <t>כמות במלאי</t>
-        </is>
-      </c>
-      <c r="N1" s="2" t="inlineStr">
-        <is>
-          <t>משקל</t>
-        </is>
-      </c>
-      <c r="O1" s="2" t="inlineStr">
-        <is>
-          <t>שפה</t>
-        </is>
-      </c>
-      <c r="P1" s="2" t="inlineStr">
-        <is>
-          <t>שם קובץ תמונה</t>
-        </is>
-      </c>
-      <c r="Q1" s="2" t="inlineStr">
-        <is>
-          <t>מוצג בדף הבית</t>
-        </is>
-      </c>
-      <c r="R1" s="2" t="inlineStr">
-        <is>
-          <t>מומלץ</t>
-        </is>
-      </c>
-      <c r="S1" s="2" t="inlineStr">
-        <is>
-          <t>חדש</t>
-        </is>
-      </c>
-      <c r="T1" s="2" t="inlineStr">
-        <is>
-          <t>פעיל</t>
+          <t>תמונה</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T10000"/>
-  <dataValidations count="2">
-    <dataValidation sqref="Q2:T10000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"כן,לא"</formula1>
-    </dataValidation>
-    <dataValidation sqref="O2:O10000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"עברית,אנגלית,יידיש,ארמית"</formula1>
-    </dataValidation>
-  </dataValidations>
+  <autoFilter ref="A1:J10000"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
@@ -1048,29 +776,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:T1"/>
+  <dimension ref="A1:J1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="28" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="34" customWidth="1" min="9" max="9"/>
-    <col width="44" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="16" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="12" customWidth="1" min="15" max="15"/>
-    <col width="22" customWidth="1" min="16" max="16"/>
-    <col width="18" customWidth="1" min="17" max="17"/>
-    <col width="12" customWidth="1" min="18" max="18"/>
-    <col width="10" customWidth="1" min="19" max="19"/>
-    <col width="10" customWidth="1" min="20" max="20"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1091,100 +809,42 @@
       </c>
       <c r="D1" s="2" t="inlineStr">
         <is>
-          <t>תת קטגוריה</t>
+          <t>מחבר / רב</t>
         </is>
       </c>
       <c r="E1" s="2" t="inlineStr">
         <is>
-          <t>קטגוריות נוספות</t>
+          <t>הוצאה לאור</t>
         </is>
       </c>
       <c r="F1" s="2" t="inlineStr">
         <is>
-          <t>מחבר</t>
-        </is>
-      </c>
-      <c r="G1" s="2" t="inlineStr">
-        <is>
-          <t>רב</t>
+          <t>תיאור</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>מחיר</t>
         </is>
       </c>
       <c r="H1" s="2" t="inlineStr">
         <is>
-          <t>הוצאה לאור</t>
+          <t>מחיר מבצע</t>
         </is>
       </c>
       <c r="I1" s="2" t="inlineStr">
         <is>
-          <t>תיאור קצר</t>
+          <t>מלאי</t>
         </is>
       </c>
       <c r="J1" s="2" t="inlineStr">
         <is>
-          <t>תיאור ארוך</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>מחיר</t>
-        </is>
-      </c>
-      <c r="L1" s="2" t="inlineStr">
-        <is>
-          <t>מחיר מבצע</t>
-        </is>
-      </c>
-      <c r="M1" s="2" t="inlineStr">
-        <is>
-          <t>כמות במלאי</t>
-        </is>
-      </c>
-      <c r="N1" s="2" t="inlineStr">
-        <is>
-          <t>משקל</t>
-        </is>
-      </c>
-      <c r="O1" s="2" t="inlineStr">
-        <is>
-          <t>שפה</t>
-        </is>
-      </c>
-      <c r="P1" s="2" t="inlineStr">
-        <is>
-          <t>שם קובץ תמונה</t>
-        </is>
-      </c>
-      <c r="Q1" s="2" t="inlineStr">
-        <is>
-          <t>מוצג בדף הבית</t>
-        </is>
-      </c>
-      <c r="R1" s="2" t="inlineStr">
-        <is>
-          <t>מומלץ</t>
-        </is>
-      </c>
-      <c r="S1" s="2" t="inlineStr">
-        <is>
-          <t>חדש</t>
-        </is>
-      </c>
-      <c r="T1" s="2" t="inlineStr">
-        <is>
-          <t>פעיל</t>
+          <t>תמונה</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T10000"/>
-  <dataValidations count="2">
-    <dataValidation sqref="Q2:T10000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"כן,לא"</formula1>
-    </dataValidation>
-    <dataValidation sqref="O2:O10000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"עברית,אנגלית,יידיש,ארמית"</formula1>
-    </dataValidation>
-  </dataValidations>
+  <autoFilter ref="A1:J10000"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
@@ -1196,29 +856,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:T1"/>
+  <dimension ref="A1:J1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="28" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="34" customWidth="1" min="9" max="9"/>
-    <col width="44" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="16" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="12" customWidth="1" min="15" max="15"/>
-    <col width="22" customWidth="1" min="16" max="16"/>
-    <col width="18" customWidth="1" min="17" max="17"/>
-    <col width="12" customWidth="1" min="18" max="18"/>
-    <col width="10" customWidth="1" min="19" max="19"/>
-    <col width="10" customWidth="1" min="20" max="20"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1239,100 +889,42 @@
       </c>
       <c r="D1" s="2" t="inlineStr">
         <is>
-          <t>תת קטגוריה</t>
+          <t>מחבר / רב</t>
         </is>
       </c>
       <c r="E1" s="2" t="inlineStr">
         <is>
-          <t>קטגוריות נוספות</t>
+          <t>הוצאה לאור</t>
         </is>
       </c>
       <c r="F1" s="2" t="inlineStr">
         <is>
-          <t>מחבר</t>
-        </is>
-      </c>
-      <c r="G1" s="2" t="inlineStr">
-        <is>
-          <t>רב</t>
+          <t>תיאור</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>מחיר</t>
         </is>
       </c>
       <c r="H1" s="2" t="inlineStr">
         <is>
-          <t>הוצאה לאור</t>
+          <t>מחיר מבצע</t>
         </is>
       </c>
       <c r="I1" s="2" t="inlineStr">
         <is>
-          <t>תיאור קצר</t>
+          <t>מלאי</t>
         </is>
       </c>
       <c r="J1" s="2" t="inlineStr">
         <is>
-          <t>תיאור ארוך</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>מחיר</t>
-        </is>
-      </c>
-      <c r="L1" s="2" t="inlineStr">
-        <is>
-          <t>מחיר מבצע</t>
-        </is>
-      </c>
-      <c r="M1" s="2" t="inlineStr">
-        <is>
-          <t>כמות במלאי</t>
-        </is>
-      </c>
-      <c r="N1" s="2" t="inlineStr">
-        <is>
-          <t>משקל</t>
-        </is>
-      </c>
-      <c r="O1" s="2" t="inlineStr">
-        <is>
-          <t>שפה</t>
-        </is>
-      </c>
-      <c r="P1" s="2" t="inlineStr">
-        <is>
-          <t>שם קובץ תמונה</t>
-        </is>
-      </c>
-      <c r="Q1" s="2" t="inlineStr">
-        <is>
-          <t>מוצג בדף הבית</t>
-        </is>
-      </c>
-      <c r="R1" s="2" t="inlineStr">
-        <is>
-          <t>מומלץ</t>
-        </is>
-      </c>
-      <c r="S1" s="2" t="inlineStr">
-        <is>
-          <t>חדש</t>
-        </is>
-      </c>
-      <c r="T1" s="2" t="inlineStr">
-        <is>
-          <t>פעיל</t>
+          <t>תמונה</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T10000"/>
-  <dataValidations count="2">
-    <dataValidation sqref="Q2:T10000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"כן,לא"</formula1>
-    </dataValidation>
-    <dataValidation sqref="O2:O10000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"עברית,אנגלית,יידיש,ארמית"</formula1>
-    </dataValidation>
-  </dataValidations>
+  <autoFilter ref="A1:J10000"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
@@ -1344,29 +936,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:T1"/>
+  <dimension ref="A1:J1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="28" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="34" customWidth="1" min="9" max="9"/>
-    <col width="44" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="16" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="12" customWidth="1" min="15" max="15"/>
-    <col width="22" customWidth="1" min="16" max="16"/>
-    <col width="18" customWidth="1" min="17" max="17"/>
-    <col width="12" customWidth="1" min="18" max="18"/>
-    <col width="10" customWidth="1" min="19" max="19"/>
-    <col width="10" customWidth="1" min="20" max="20"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1387,100 +969,42 @@
       </c>
       <c r="D1" s="2" t="inlineStr">
         <is>
-          <t>תת קטגוריה</t>
+          <t>מחבר / רב</t>
         </is>
       </c>
       <c r="E1" s="2" t="inlineStr">
         <is>
-          <t>קטגוריות נוספות</t>
+          <t>הוצאה לאור</t>
         </is>
       </c>
       <c r="F1" s="2" t="inlineStr">
         <is>
-          <t>מחבר</t>
-        </is>
-      </c>
-      <c r="G1" s="2" t="inlineStr">
-        <is>
-          <t>רב</t>
+          <t>תיאור</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>מחיר</t>
         </is>
       </c>
       <c r="H1" s="2" t="inlineStr">
         <is>
-          <t>הוצאה לאור</t>
+          <t>מחיר מבצע</t>
         </is>
       </c>
       <c r="I1" s="2" t="inlineStr">
         <is>
-          <t>תיאור קצר</t>
+          <t>מלאי</t>
         </is>
       </c>
       <c r="J1" s="2" t="inlineStr">
         <is>
-          <t>תיאור ארוך</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>מחיר</t>
-        </is>
-      </c>
-      <c r="L1" s="2" t="inlineStr">
-        <is>
-          <t>מחיר מבצע</t>
-        </is>
-      </c>
-      <c r="M1" s="2" t="inlineStr">
-        <is>
-          <t>כמות במלאי</t>
-        </is>
-      </c>
-      <c r="N1" s="2" t="inlineStr">
-        <is>
-          <t>משקל</t>
-        </is>
-      </c>
-      <c r="O1" s="2" t="inlineStr">
-        <is>
-          <t>שפה</t>
-        </is>
-      </c>
-      <c r="P1" s="2" t="inlineStr">
-        <is>
-          <t>שם קובץ תמונה</t>
-        </is>
-      </c>
-      <c r="Q1" s="2" t="inlineStr">
-        <is>
-          <t>מוצג בדף הבית</t>
-        </is>
-      </c>
-      <c r="R1" s="2" t="inlineStr">
-        <is>
-          <t>מומלץ</t>
-        </is>
-      </c>
-      <c r="S1" s="2" t="inlineStr">
-        <is>
-          <t>חדש</t>
-        </is>
-      </c>
-      <c r="T1" s="2" t="inlineStr">
-        <is>
-          <t>פעיל</t>
+          <t>תמונה</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T10000"/>
-  <dataValidations count="2">
-    <dataValidation sqref="Q2:T10000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"כן,לא"</formula1>
-    </dataValidation>
-    <dataValidation sqref="O2:O10000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"עברית,אנגלית,יידיש,ארמית"</formula1>
-    </dataValidation>
-  </dataValidations>
+  <autoFilter ref="A1:J10000"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
@@ -1492,29 +1016,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:T1"/>
+  <dimension ref="A1:J1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="28" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="34" customWidth="1" min="9" max="9"/>
-    <col width="44" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="16" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="12" customWidth="1" min="15" max="15"/>
-    <col width="22" customWidth="1" min="16" max="16"/>
-    <col width="18" customWidth="1" min="17" max="17"/>
-    <col width="12" customWidth="1" min="18" max="18"/>
-    <col width="10" customWidth="1" min="19" max="19"/>
-    <col width="10" customWidth="1" min="20" max="20"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1535,100 +1049,42 @@
       </c>
       <c r="D1" s="2" t="inlineStr">
         <is>
-          <t>תת קטגוריה</t>
+          <t>מחבר / רב</t>
         </is>
       </c>
       <c r="E1" s="2" t="inlineStr">
         <is>
-          <t>קטגוריות נוספות</t>
+          <t>הוצאה לאור</t>
         </is>
       </c>
       <c r="F1" s="2" t="inlineStr">
         <is>
-          <t>מחבר</t>
-        </is>
-      </c>
-      <c r="G1" s="2" t="inlineStr">
-        <is>
-          <t>רב</t>
+          <t>תיאור</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>מחיר</t>
         </is>
       </c>
       <c r="H1" s="2" t="inlineStr">
         <is>
-          <t>הוצאה לאור</t>
+          <t>מחיר מבצע</t>
         </is>
       </c>
       <c r="I1" s="2" t="inlineStr">
         <is>
-          <t>תיאור קצר</t>
+          <t>מלאי</t>
         </is>
       </c>
       <c r="J1" s="2" t="inlineStr">
         <is>
-          <t>תיאור ארוך</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>מחיר</t>
-        </is>
-      </c>
-      <c r="L1" s="2" t="inlineStr">
-        <is>
-          <t>מחיר מבצע</t>
-        </is>
-      </c>
-      <c r="M1" s="2" t="inlineStr">
-        <is>
-          <t>כמות במלאי</t>
-        </is>
-      </c>
-      <c r="N1" s="2" t="inlineStr">
-        <is>
-          <t>משקל</t>
-        </is>
-      </c>
-      <c r="O1" s="2" t="inlineStr">
-        <is>
-          <t>שפה</t>
-        </is>
-      </c>
-      <c r="P1" s="2" t="inlineStr">
-        <is>
-          <t>שם קובץ תמונה</t>
-        </is>
-      </c>
-      <c r="Q1" s="2" t="inlineStr">
-        <is>
-          <t>מוצג בדף הבית</t>
-        </is>
-      </c>
-      <c r="R1" s="2" t="inlineStr">
-        <is>
-          <t>מומלץ</t>
-        </is>
-      </c>
-      <c r="S1" s="2" t="inlineStr">
-        <is>
-          <t>חדש</t>
-        </is>
-      </c>
-      <c r="T1" s="2" t="inlineStr">
-        <is>
-          <t>פעיל</t>
+          <t>תמונה</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T10000"/>
-  <dataValidations count="2">
-    <dataValidation sqref="Q2:T10000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"כן,לא"</formula1>
-    </dataValidation>
-    <dataValidation sqref="O2:O10000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"עברית,אנגלית,יידיש,ארמית"</formula1>
-    </dataValidation>
-  </dataValidations>
+  <autoFilter ref="A1:J10000"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/public/templates/otzar_hakodesh_books_import_template.xlsx
+++ b/public/templates/otzar_hakodesh_books_import_template.xlsx
@@ -459,7 +459,7 @@
   <dimension ref="A1:J1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="32" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
@@ -468,13 +468,13 @@
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>מק"ט</t>
+          <t>מספר</t>
         </is>
       </c>
       <c r="B1" s="2" t="inlineStr">
@@ -519,7 +519,7 @@
       </c>
       <c r="J1" s="2" t="inlineStr">
         <is>
-          <t>תמונה</t>
+          <t>מספר תמונה</t>
         </is>
       </c>
     </row>
@@ -539,7 +539,7 @@
   <dimension ref="A1:J1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="32" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
@@ -548,13 +548,13 @@
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>מק"ט</t>
+          <t>מספר</t>
         </is>
       </c>
       <c r="B1" s="2" t="inlineStr">
@@ -599,7 +599,7 @@
       </c>
       <c r="J1" s="2" t="inlineStr">
         <is>
-          <t>תמונה</t>
+          <t>מספר תמונה</t>
         </is>
       </c>
     </row>
@@ -619,7 +619,7 @@
   <dimension ref="A1:J1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="32" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
@@ -628,13 +628,13 @@
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>מק"ט</t>
+          <t>מספר</t>
         </is>
       </c>
       <c r="B1" s="2" t="inlineStr">
@@ -679,7 +679,7 @@
       </c>
       <c r="J1" s="2" t="inlineStr">
         <is>
-          <t>תמונה</t>
+          <t>מספר תמונה</t>
         </is>
       </c>
     </row>
@@ -699,7 +699,7 @@
   <dimension ref="A1:J1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="32" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
@@ -708,13 +708,13 @@
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>מק"ט</t>
+          <t>מספר</t>
         </is>
       </c>
       <c r="B1" s="2" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="J1" s="2" t="inlineStr">
         <is>
-          <t>תמונה</t>
+          <t>מספר תמונה</t>
         </is>
       </c>
     </row>
@@ -779,7 +779,7 @@
   <dimension ref="A1:J1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="32" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
@@ -788,13 +788,13 @@
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>מק"ט</t>
+          <t>מספר</t>
         </is>
       </c>
       <c r="B1" s="2" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="J1" s="2" t="inlineStr">
         <is>
-          <t>תמונה</t>
+          <t>מספר תמונה</t>
         </is>
       </c>
     </row>
@@ -859,7 +859,7 @@
   <dimension ref="A1:J1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="32" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
@@ -868,13 +868,13 @@
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>מק"ט</t>
+          <t>מספר</t>
         </is>
       </c>
       <c r="B1" s="2" t="inlineStr">
@@ -919,7 +919,7 @@
       </c>
       <c r="J1" s="2" t="inlineStr">
         <is>
-          <t>תמונה</t>
+          <t>מספר תמונה</t>
         </is>
       </c>
     </row>
@@ -939,7 +939,7 @@
   <dimension ref="A1:J1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="32" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
@@ -948,13 +948,13 @@
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>מק"ט</t>
+          <t>מספר</t>
         </is>
       </c>
       <c r="B1" s="2" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="J1" s="2" t="inlineStr">
         <is>
-          <t>תמונה</t>
+          <t>מספר תמונה</t>
         </is>
       </c>
     </row>
@@ -1019,7 +1019,7 @@
   <dimension ref="A1:J1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="32" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
@@ -1028,13 +1028,13 @@
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>מק"ט</t>
+          <t>מספר</t>
         </is>
       </c>
       <c r="B1" s="2" t="inlineStr">
@@ -1079,7 +1079,7 @@
       </c>
       <c r="J1" s="2" t="inlineStr">
         <is>
-          <t>תמונה</t>
+          <t>מספר תמונה</t>
         </is>
       </c>
     </row>
